--- a/artfynd/A 22782-2026 artfynd.xlsx
+++ b/artfynd/A 22782-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,9636 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133575969</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>396453</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6763380</v>
+      </c>
+      <c r="S4" t="n">
+        <v>31</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133575981</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>396453</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6763448</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133576002</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>396399</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6763573</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133576029</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>396331</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6763518</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133575989</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>396482</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6763495</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133575949</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>396524</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6763269</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133575973</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>396430</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6763401</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133576049</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>396397</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6763265</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133575968</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>396469</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6763378</v>
+      </c>
+      <c r="S12" t="n">
+        <v>21</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133576032</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>396379</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6763458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133575998</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>396426</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6763563</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133576063</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>396193</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6763033</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133575956</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>396487</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6763296</v>
+      </c>
+      <c r="S16" t="n">
+        <v>28</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133575987</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>396478</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6763495</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133575952</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>396487</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6763276</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133576068</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>396300</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6762998</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133576034</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>396386</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6763437</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133576003</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>396387</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6763575</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133576030</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>396360</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6763487</v>
+      </c>
+      <c r="S22" t="n">
+        <v>51</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133576004</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>396364</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6763588</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133575971</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>396434</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6763391</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133576067</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>396289</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6763002</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133576069</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>396297</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6762989</v>
+      </c>
+      <c r="S26" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133576055</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>396289</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6763159</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133576037</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>396403</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6763437</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133575960</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>396487</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6763334</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133576066</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>396278</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6763006</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133576065</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>396276</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6763004</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133575970</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>396448</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6763384</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133575974</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>396426</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6763408</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133575963</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>396488</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6763387</v>
+      </c>
+      <c r="S34" t="n">
+        <v>22</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133575950</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>396504</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6763271</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133576056</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>396204</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6763126</v>
+      </c>
+      <c r="S36" t="n">
+        <v>14</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133576071</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>396310</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6762958</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133575999</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78340</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>396410</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6763572</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133576052</v>
+      </c>
+      <c r="B39" t="n">
+        <v>81318</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>396385</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6763240</v>
+      </c>
+      <c r="S39" t="n">
+        <v>26</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133575958</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>396497</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6763304</v>
+      </c>
+      <c r="S40" t="n">
+        <v>14</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133575964</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>396477</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6763372</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133575977</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>396433</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6763424</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133576059</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>396159</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6763076</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133576058</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>396184</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6763111</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133575991</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78340</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>396482</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6763495</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133576050</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>396392</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6763248</v>
+      </c>
+      <c r="S46" t="n">
+        <v>18</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133575953</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>396486</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6763277</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>133576057</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>396242</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6763146</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>133575957</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>396490</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6763306</v>
+      </c>
+      <c r="S49" t="n">
+        <v>19</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>133575993</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>396451</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6763508</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133575955</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79357</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>396488</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6763293</v>
+      </c>
+      <c r="S51" t="n">
+        <v>6</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133575959</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>185</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>396502</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6763304</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133575992</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>396468</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6763503</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133576051</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>353</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>396390</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6763254</v>
+      </c>
+      <c r="S54" t="n">
+        <v>17</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133575980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>396452</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6763447</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133575947</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>396542</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6763282</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133576061</v>
+      </c>
+      <c r="B57" t="n">
+        <v>81318</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>396175</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6763055</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133575975</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>396429</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6763411</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133575978</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>396447</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6763436</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133576073</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>396343</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6763025</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133575951</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>396498</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6763262</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133575965</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>396474</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6763373</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133576001</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>396405</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6763572</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133576000</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>396407</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6763575</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>133575994</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>396439</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6763508</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>133576033</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>353</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>396386</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6763437</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>133576005</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>396349</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6763575</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133575984</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>396445</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6763456</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133576075</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>396346</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6763061</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133576031</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>396375</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6763463</v>
+      </c>
+      <c r="S70" t="n">
+        <v>22</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>133575976</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>396433</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6763412</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133575986</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>396455</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6763482</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>133575990</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>396482</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6763496</v>
+      </c>
+      <c r="S73" t="n">
+        <v>9</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>133576072</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>396322</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6762975</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>133575966</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>396495</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6763422</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>133575983</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>396469</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6763460</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>133575995</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>396433</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6763522</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133576036</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>396401</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6763437</v>
+      </c>
+      <c r="S78" t="n">
+        <v>8</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133575972</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>396434</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6763395</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>133575961</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79357</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>396468</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6763343</v>
+      </c>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>133576060</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>396160</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6763070</v>
+      </c>
+      <c r="S81" t="n">
+        <v>17</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>133576062</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>396183</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6763040</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>133575962</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>396491</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6763390</v>
+      </c>
+      <c r="S83" t="n">
+        <v>20</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>133575967</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79357</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>396474</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6763373</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>133575996</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79357</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>396433</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6763546</v>
+      </c>
+      <c r="S85" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>133576054</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>396310</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6763166</v>
+      </c>
+      <c r="S86" t="n">
+        <v>7</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>133575997</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>396428</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6763551</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>133575979</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>396449</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6763444</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>133576064</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>396223</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6762996</v>
+      </c>
+      <c r="S89" t="n">
+        <v>45</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>133575954</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>396484</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6763285</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>133575948</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>353</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>396527</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6763278</v>
+      </c>
+      <c r="S91" t="n">
+        <v>55</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>133575985</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>396448</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6763476</v>
+      </c>
+      <c r="S92" t="n">
+        <v>11</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>133575982</v>
+      </c>
+      <c r="B93" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>353</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>396453</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6763453</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22782-2026 artfynd.xlsx
+++ b/artfynd/A 22782-2026 artfynd.xlsx
@@ -934,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133575969</v>
+        <v>133575981</v>
       </c>
       <c r="B4" t="n">
         <v>79952</v>
@@ -972,10 +972,10 @@
         <v>396453</v>
       </c>
       <c r="R4" t="n">
-        <v>6763380</v>
+        <v>6763448</v>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133575981</v>
+        <v>133575989</v>
       </c>
       <c r="B5" t="n">
         <v>79952</v>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396453</v>
+        <v>396482</v>
       </c>
       <c r="R5" t="n">
-        <v>6763448</v>
+        <v>6763495</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133576002</v>
+        <v>133575969</v>
       </c>
       <c r="B6" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396399</v>
+        <v>396453</v>
       </c>
       <c r="R6" t="n">
-        <v>6763573</v>
+        <v>6763380</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133575989</v>
+        <v>133576002</v>
       </c>
       <c r="B8" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396482</v>
+        <v>396399</v>
       </c>
       <c r="R8" t="n">
-        <v>6763495</v>
+        <v>6763573</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133575949</v>
+        <v>133575968</v>
       </c>
       <c r="B9" t="n">
-        <v>79952</v>
+        <v>78999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396524</v>
+        <v>396469</v>
       </c>
       <c r="R9" t="n">
-        <v>6763269</v>
+        <v>6763378</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133575968</v>
+        <v>133575949</v>
       </c>
       <c r="B12" t="n">
-        <v>78999</v>
+        <v>79952</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>396469</v>
+        <v>396524</v>
       </c>
       <c r="R12" t="n">
-        <v>6763378</v>
+        <v>6763269</v>
       </c>
       <c r="S12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133576032</v>
+        <v>133575998</v>
       </c>
       <c r="B13" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>396379</v>
+        <v>396426</v>
       </c>
       <c r="R13" t="n">
-        <v>6763458</v>
+        <v>6763563</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133575998</v>
+        <v>133576032</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396426</v>
+        <v>396379</v>
       </c>
       <c r="R14" t="n">
-        <v>6763563</v>
+        <v>6763458</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133576063</v>
+        <v>133575956</v>
       </c>
       <c r="B15" t="n">
         <v>79333</v>
@@ -2146,13 +2146,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396193</v>
+        <v>396487</v>
       </c>
       <c r="R15" t="n">
-        <v>6763033</v>
+        <v>6763296</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,7 +2218,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133575956</v>
+        <v>133576063</v>
       </c>
       <c r="B16" t="n">
         <v>79333</v>
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396487</v>
+        <v>396193</v>
       </c>
       <c r="R16" t="n">
-        <v>6763296</v>
+        <v>6763033</v>
       </c>
       <c r="S16" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133575952</v>
+        <v>133576068</v>
       </c>
       <c r="B18" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396487</v>
+        <v>396300</v>
       </c>
       <c r="R18" t="n">
-        <v>6763276</v>
+        <v>6762998</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,7 +2539,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133576068</v>
+        <v>133576034</v>
       </c>
       <c r="B19" t="n">
         <v>79952</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396300</v>
+        <v>396386</v>
       </c>
       <c r="R19" t="n">
-        <v>6762998</v>
+        <v>6763437</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133576034</v>
+        <v>133576003</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396386</v>
+        <v>396387</v>
       </c>
       <c r="R20" t="n">
-        <v>6763437</v>
+        <v>6763575</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133576003</v>
+        <v>133575952</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,21 +2764,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>396387</v>
+        <v>396487</v>
       </c>
       <c r="R21" t="n">
-        <v>6763575</v>
+        <v>6763276</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133576030</v>
+        <v>133576004</v>
       </c>
       <c r="B22" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,21 +2871,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396360</v>
+        <v>396364</v>
       </c>
       <c r="R22" t="n">
-        <v>6763487</v>
+        <v>6763588</v>
       </c>
       <c r="S22" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133576004</v>
+        <v>133576030</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396364</v>
+        <v>396360</v>
       </c>
       <c r="R23" t="n">
-        <v>6763588</v>
+        <v>6763487</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,7 +3074,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133575971</v>
+        <v>133576069</v>
       </c>
       <c r="B24" t="n">
         <v>79952</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>396434</v>
+        <v>396297</v>
       </c>
       <c r="R24" t="n">
-        <v>6763391</v>
+        <v>6762989</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133576067</v>
+        <v>133575960</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>396289</v>
+        <v>396487</v>
       </c>
       <c r="R25" t="n">
-        <v>6763002</v>
+        <v>6763334</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,7 +3288,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133576069</v>
+        <v>133575971</v>
       </c>
       <c r="B26" t="n">
         <v>79952</v>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>396297</v>
+        <v>396434</v>
       </c>
       <c r="R26" t="n">
-        <v>6762989</v>
+        <v>6763391</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133576037</v>
+        <v>133576067</v>
       </c>
       <c r="B28" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>396403</v>
+        <v>396289</v>
       </c>
       <c r="R28" t="n">
-        <v>6763437</v>
+        <v>6763002</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,7 +3609,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133575960</v>
+        <v>133576037</v>
       </c>
       <c r="B29" t="n">
         <v>79952</v>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>396487</v>
+        <v>396403</v>
       </c>
       <c r="R29" t="n">
-        <v>6763334</v>
+        <v>6763437</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3716,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133576066</v>
+        <v>133576056</v>
       </c>
       <c r="B30" t="n">
         <v>79923</v>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396278</v>
+        <v>396204</v>
       </c>
       <c r="R30" t="n">
-        <v>6763006</v>
+        <v>6763126</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133576065</v>
+        <v>133575963</v>
       </c>
       <c r="B31" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,21 +3834,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396276</v>
+        <v>396488</v>
       </c>
       <c r="R31" t="n">
-        <v>6763004</v>
+        <v>6763387</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133575970</v>
+        <v>133576066</v>
       </c>
       <c r="B32" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3941,21 +3941,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396448</v>
+        <v>396278</v>
       </c>
       <c r="R32" t="n">
-        <v>6763384</v>
+        <v>6763006</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,7 +4037,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133575974</v>
+        <v>133575950</v>
       </c>
       <c r="B33" t="n">
         <v>79952</v>
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396426</v>
+        <v>396504</v>
       </c>
       <c r="R33" t="n">
-        <v>6763408</v>
+        <v>6763271</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133575963</v>
+        <v>133576065</v>
       </c>
       <c r="B34" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,13 +4179,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396488</v>
+        <v>396276</v>
       </c>
       <c r="R34" t="n">
-        <v>6763387</v>
+        <v>6763004</v>
       </c>
       <c r="S34" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4251,7 +4251,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133575950</v>
+        <v>133575974</v>
       </c>
       <c r="B35" t="n">
         <v>79952</v>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396504</v>
+        <v>396426</v>
       </c>
       <c r="R35" t="n">
-        <v>6763271</v>
+        <v>6763408</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133576056</v>
+        <v>133575970</v>
       </c>
       <c r="B36" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4369,21 +4369,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>396204</v>
+        <v>396448</v>
       </c>
       <c r="R36" t="n">
-        <v>6763126</v>
+        <v>6763384</v>
       </c>
       <c r="S36" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4465,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133576071</v>
+        <v>133576052</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>81318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4500,13 +4500,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>396310</v>
+        <v>396385</v>
       </c>
       <c r="R37" t="n">
-        <v>6762958</v>
+        <v>6763240</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133576052</v>
+        <v>133576071</v>
       </c>
       <c r="B39" t="n">
-        <v>81318</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396385</v>
+        <v>396310</v>
       </c>
       <c r="R39" t="n">
-        <v>6763240</v>
+        <v>6762958</v>
       </c>
       <c r="S39" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133575958</v>
+        <v>133575977</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396497</v>
+        <v>396433</v>
       </c>
       <c r="R40" t="n">
-        <v>6763304</v>
+        <v>6763424</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133575964</v>
+        <v>133575958</v>
       </c>
       <c r="B41" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396477</v>
+        <v>396497</v>
       </c>
       <c r="R41" t="n">
-        <v>6763372</v>
+        <v>6763304</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5000,10 +5000,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133575977</v>
+        <v>133575964</v>
       </c>
       <c r="B42" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396433</v>
+        <v>396477</v>
       </c>
       <c r="R42" t="n">
-        <v>6763424</v>
+        <v>6763372</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5107,10 +5107,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133576059</v>
+        <v>133576050</v>
       </c>
       <c r="B43" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5142,13 +5142,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396159</v>
+        <v>396392</v>
       </c>
       <c r="R43" t="n">
-        <v>6763076</v>
+        <v>6763248</v>
       </c>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133576058</v>
+        <v>133575953</v>
       </c>
       <c r="B44" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5225,21 +5225,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5249,13 +5249,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396184</v>
+        <v>396486</v>
       </c>
       <c r="R44" t="n">
-        <v>6763111</v>
+        <v>6763277</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,7 +5428,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133576050</v>
+        <v>133576057</v>
       </c>
       <c r="B46" t="n">
         <v>79333</v>
@@ -5463,13 +5463,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396392</v>
+        <v>396242</v>
       </c>
       <c r="R46" t="n">
-        <v>6763248</v>
+        <v>6763146</v>
       </c>
       <c r="S46" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133575953</v>
+        <v>133576059</v>
       </c>
       <c r="B47" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396486</v>
+        <v>396159</v>
       </c>
       <c r="R47" t="n">
-        <v>6763277</v>
+        <v>6763076</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133576057</v>
+        <v>133576058</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396242</v>
+        <v>396184</v>
       </c>
       <c r="R48" t="n">
-        <v>6763146</v>
+        <v>6763111</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5749,32 +5749,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133575957</v>
+        <v>133575955</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>79357</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5784,13 +5784,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396490</v>
+        <v>396488</v>
       </c>
       <c r="R49" t="n">
-        <v>6763306</v>
+        <v>6763293</v>
       </c>
       <c r="S49" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5963,32 +5963,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133575955</v>
+        <v>133575957</v>
       </c>
       <c r="B51" t="n">
-        <v>79357</v>
+        <v>79952</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>396488</v>
+        <v>396490</v>
       </c>
       <c r="R51" t="n">
-        <v>6763293</v>
+        <v>6763306</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6070,10 +6070,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133575959</v>
+        <v>133575978</v>
       </c>
       <c r="B52" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>396502</v>
+        <v>396447</v>
       </c>
       <c r="R52" t="n">
-        <v>6763304</v>
+        <v>6763436</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,7 +6177,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133575992</v>
+        <v>133575947</v>
       </c>
       <c r="B53" t="n">
         <v>79333</v>
@@ -6212,13 +6212,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>396468</v>
+        <v>396542</v>
       </c>
       <c r="R53" t="n">
-        <v>6763503</v>
+        <v>6763282</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133576051</v>
+        <v>133575992</v>
       </c>
       <c r="B54" t="n">
-        <v>78999</v>
+        <v>79333</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>396390</v>
+        <v>396468</v>
       </c>
       <c r="R54" t="n">
-        <v>6763254</v>
+        <v>6763503</v>
       </c>
       <c r="S54" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133575980</v>
+        <v>133575975</v>
       </c>
       <c r="B55" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,21 +6402,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6426,13 +6426,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>396452</v>
+        <v>396429</v>
       </c>
       <c r="R55" t="n">
-        <v>6763447</v>
+        <v>6763411</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133575947</v>
+        <v>133575959</v>
       </c>
       <c r="B56" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6509,21 +6509,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>396542</v>
+        <v>396502</v>
       </c>
       <c r="R56" t="n">
-        <v>6763282</v>
+        <v>6763304</v>
       </c>
       <c r="S56" t="n">
         <v>6</v>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6605,10 +6605,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133576061</v>
+        <v>133576051</v>
       </c>
       <c r="B57" t="n">
-        <v>81318</v>
+        <v>78999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6616,21 +6616,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>396175</v>
+        <v>396390</v>
       </c>
       <c r="R57" t="n">
-        <v>6763055</v>
+        <v>6763254</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133575975</v>
+        <v>133576061</v>
       </c>
       <c r="B58" t="n">
-        <v>79333</v>
+        <v>81318</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6747,13 +6747,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>396429</v>
+        <v>396175</v>
       </c>
       <c r="R58" t="n">
-        <v>6763411</v>
+        <v>6763055</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6819,10 +6819,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133575978</v>
+        <v>133575980</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6830,21 +6830,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>396447</v>
+        <v>396452</v>
       </c>
       <c r="R59" t="n">
-        <v>6763436</v>
+        <v>6763447</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133575951</v>
+        <v>133575965</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7068,13 +7068,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>396498</v>
+        <v>396474</v>
       </c>
       <c r="R61" t="n">
-        <v>6763262</v>
+        <v>6763373</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133575965</v>
+        <v>133575951</v>
       </c>
       <c r="B62" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7151,21 +7151,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>396474</v>
+        <v>396498</v>
       </c>
       <c r="R62" t="n">
-        <v>6763373</v>
+        <v>6763262</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7354,10 +7354,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133576000</v>
+        <v>133576033</v>
       </c>
       <c r="B64" t="n">
-        <v>79923</v>
+        <v>78999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7365,21 +7365,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>396407</v>
+        <v>396386</v>
       </c>
       <c r="R64" t="n">
-        <v>6763575</v>
+        <v>6763437</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7461,10 +7461,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133575994</v>
+        <v>133576000</v>
       </c>
       <c r="B65" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7472,21 +7472,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396439</v>
+        <v>396407</v>
       </c>
       <c r="R65" t="n">
-        <v>6763508</v>
+        <v>6763575</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,10 +7568,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133576033</v>
+        <v>133575984</v>
       </c>
       <c r="B66" t="n">
-        <v>78999</v>
+        <v>79333</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7579,21 +7579,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396386</v>
+        <v>396445</v>
       </c>
       <c r="R66" t="n">
-        <v>6763437</v>
+        <v>6763456</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,7 +7675,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133576005</v>
+        <v>133575994</v>
       </c>
       <c r="B67" t="n">
         <v>79952</v>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>396349</v>
+        <v>396439</v>
       </c>
       <c r="R67" t="n">
-        <v>6763575</v>
+        <v>6763508</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133575984</v>
+        <v>133576005</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7793,21 +7793,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>396445</v>
+        <v>396349</v>
       </c>
       <c r="R68" t="n">
-        <v>6763456</v>
+        <v>6763575</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7889,7 +7889,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133576075</v>
+        <v>133576031</v>
       </c>
       <c r="B69" t="n">
         <v>79333</v>
@@ -7924,13 +7924,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>396346</v>
+        <v>396375</v>
       </c>
       <c r="R69" t="n">
-        <v>6763061</v>
+        <v>6763463</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,7 +7996,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133576031</v>
+        <v>133576075</v>
       </c>
       <c r="B70" t="n">
         <v>79333</v>
@@ -8031,13 +8031,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>396375</v>
+        <v>396346</v>
       </c>
       <c r="R70" t="n">
-        <v>6763463</v>
+        <v>6763061</v>
       </c>
       <c r="S70" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,7 +8103,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133575976</v>
+        <v>133575986</v>
       </c>
       <c r="B71" t="n">
         <v>79952</v>
@@ -8138,13 +8138,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>396433</v>
+        <v>396455</v>
       </c>
       <c r="R71" t="n">
-        <v>6763412</v>
+        <v>6763482</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8210,7 +8210,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133575986</v>
+        <v>133575976</v>
       </c>
       <c r="B72" t="n">
         <v>79952</v>
@@ -8245,13 +8245,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396455</v>
+        <v>396433</v>
       </c>
       <c r="R72" t="n">
-        <v>6763482</v>
+        <v>6763412</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8317,32 +8317,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133575990</v>
+        <v>133575966</v>
       </c>
       <c r="B73" t="n">
-        <v>79091</v>
+        <v>57145</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396482</v>
+        <v>396495</v>
       </c>
       <c r="R73" t="n">
-        <v>6763496</v>
+        <v>6763422</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,10 +8424,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133576072</v>
+        <v>133576036</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8435,21 +8435,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>396322</v>
+        <v>396401</v>
       </c>
       <c r="R74" t="n">
-        <v>6762975</v>
+        <v>6763437</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8531,10 +8531,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133575966</v>
+        <v>133575961</v>
       </c>
       <c r="B75" t="n">
-        <v>57145</v>
+        <v>79357</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8542,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>396495</v>
+        <v>396468</v>
       </c>
       <c r="R75" t="n">
-        <v>6763422</v>
+        <v>6763343</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8638,7 +8638,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133575983</v>
+        <v>133576060</v>
       </c>
       <c r="B76" t="n">
         <v>79333</v>
@@ -8673,13 +8673,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>396469</v>
+        <v>396160</v>
       </c>
       <c r="R76" t="n">
-        <v>6763460</v>
+        <v>6763070</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,7 +8745,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133575995</v>
+        <v>133575983</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8780,13 +8780,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>396433</v>
+        <v>396469</v>
       </c>
       <c r="R77" t="n">
-        <v>6763522</v>
+        <v>6763460</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,10 +8852,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133576036</v>
+        <v>133576072</v>
       </c>
       <c r="B78" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8863,21 +8863,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>396401</v>
+        <v>396322</v>
       </c>
       <c r="R78" t="n">
-        <v>6763437</v>
+        <v>6762975</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,7 +8959,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133575972</v>
+        <v>133576062</v>
       </c>
       <c r="B79" t="n">
         <v>79333</v>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396434</v>
+        <v>396183</v>
       </c>
       <c r="R79" t="n">
-        <v>6763395</v>
+        <v>6763040</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9066,32 +9066,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133575961</v>
+        <v>133575995</v>
       </c>
       <c r="B80" t="n">
-        <v>79357</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9101,13 +9101,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396468</v>
+        <v>396433</v>
       </c>
       <c r="R80" t="n">
-        <v>6763343</v>
+        <v>6763522</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9173,7 +9173,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133576060</v>
+        <v>133575972</v>
       </c>
       <c r="B81" t="n">
         <v>79333</v>
@@ -9208,13 +9208,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>396160</v>
+        <v>396434</v>
       </c>
       <c r="R81" t="n">
-        <v>6763070</v>
+        <v>6763395</v>
       </c>
       <c r="S81" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9280,10 +9280,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133576062</v>
+        <v>133575990</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9291,21 +9291,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,13 +9315,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>396183</v>
+        <v>396482</v>
       </c>
       <c r="R82" t="n">
-        <v>6763040</v>
+        <v>6763496</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9387,10 +9387,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133575962</v>
+        <v>133576064</v>
       </c>
       <c r="B83" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9398,21 +9398,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9422,13 +9422,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>396491</v>
+        <v>396223</v>
       </c>
       <c r="R83" t="n">
-        <v>6763390</v>
+        <v>6762996</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9494,32 +9494,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133575967</v>
+        <v>133575997</v>
       </c>
       <c r="B84" t="n">
-        <v>79357</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>396474</v>
+        <v>396428</v>
       </c>
       <c r="R84" t="n">
-        <v>6763373</v>
+        <v>6763551</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9601,32 +9601,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133575996</v>
+        <v>133576054</v>
       </c>
       <c r="B85" t="n">
-        <v>79357</v>
+        <v>79333</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>396433</v>
+        <v>396310</v>
       </c>
       <c r="R85" t="n">
-        <v>6763546</v>
+        <v>6763166</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9708,7 +9708,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133576054</v>
+        <v>133575979</v>
       </c>
       <c r="B86" t="n">
         <v>79333</v>
@@ -9743,13 +9743,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>396310</v>
+        <v>396449</v>
       </c>
       <c r="R86" t="n">
-        <v>6763166</v>
+        <v>6763444</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9815,32 +9815,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133575997</v>
+        <v>133575996</v>
       </c>
       <c r="B87" t="n">
-        <v>79333</v>
+        <v>79357</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9850,13 +9850,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>396428</v>
+        <v>396433</v>
       </c>
       <c r="R87" t="n">
-        <v>6763551</v>
+        <v>6763546</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9922,32 +9922,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133575979</v>
+        <v>133575967</v>
       </c>
       <c r="B88" t="n">
-        <v>79333</v>
+        <v>79357</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>396449</v>
+        <v>396474</v>
       </c>
       <c r="R88" t="n">
-        <v>6763444</v>
+        <v>6763373</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10029,10 +10029,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133576064</v>
+        <v>133575962</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10040,21 +10040,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>396223</v>
+        <v>396491</v>
       </c>
       <c r="R89" t="n">
-        <v>6762996</v>
+        <v>6763390</v>
       </c>
       <c r="S89" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10243,10 +10243,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133575948</v>
+        <v>133575985</v>
       </c>
       <c r="B91" t="n">
-        <v>78999</v>
+        <v>79333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10254,21 +10254,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10278,13 +10278,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>396527</v>
+        <v>396448</v>
       </c>
       <c r="R91" t="n">
-        <v>6763278</v>
+        <v>6763476</v>
       </c>
       <c r="S91" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10350,10 +10350,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133575985</v>
+        <v>133575982</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>78999</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10361,21 +10361,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>396448</v>
+        <v>396453</v>
       </c>
       <c r="R92" t="n">
-        <v>6763476</v>
+        <v>6763453</v>
       </c>
       <c r="S92" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10457,7 +10457,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133575982</v>
+        <v>133575948</v>
       </c>
       <c r="B93" t="n">
         <v>78999</v>
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>396453</v>
+        <v>396527</v>
       </c>
       <c r="R93" t="n">
-        <v>6763453</v>
+        <v>6763278</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD93" t="b">

--- a/artfynd/A 22782-2026 artfynd.xlsx
+++ b/artfynd/A 22782-2026 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133576029</v>
+        <v>133576002</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396331</v>
+        <v>396399</v>
       </c>
       <c r="R7" t="n">
-        <v>6763518</v>
+        <v>6763573</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133576002</v>
+        <v>133576029</v>
       </c>
       <c r="B8" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396399</v>
+        <v>396331</v>
       </c>
       <c r="R8" t="n">
-        <v>6763573</v>
+        <v>6763518</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133575973</v>
+        <v>133575949</v>
       </c>
       <c r="B10" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>396430</v>
+        <v>396524</v>
       </c>
       <c r="R10" t="n">
-        <v>6763401</v>
+        <v>6763269</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133575949</v>
+        <v>133575973</v>
       </c>
       <c r="B12" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>396524</v>
+        <v>396430</v>
       </c>
       <c r="R12" t="n">
-        <v>6763269</v>
+        <v>6763401</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133575998</v>
+        <v>133576032</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>396426</v>
+        <v>396379</v>
       </c>
       <c r="R13" t="n">
-        <v>6763563</v>
+        <v>6763458</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133576032</v>
+        <v>133575998</v>
       </c>
       <c r="B14" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396379</v>
+        <v>396426</v>
       </c>
       <c r="R14" t="n">
-        <v>6763458</v>
+        <v>6763563</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133576068</v>
+        <v>133576003</v>
       </c>
       <c r="B18" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396300</v>
+        <v>396387</v>
       </c>
       <c r="R18" t="n">
-        <v>6762998</v>
+        <v>6763575</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,7 +2539,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133576034</v>
+        <v>133576068</v>
       </c>
       <c r="B19" t="n">
         <v>79952</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396386</v>
+        <v>396300</v>
       </c>
       <c r="R19" t="n">
-        <v>6763437</v>
+        <v>6762998</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133576003</v>
+        <v>133576034</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396387</v>
+        <v>396386</v>
       </c>
       <c r="R20" t="n">
-        <v>6763575</v>
+        <v>6763437</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133576004</v>
+        <v>133576030</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,21 +2871,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396364</v>
+        <v>396360</v>
       </c>
       <c r="R22" t="n">
-        <v>6763588</v>
+        <v>6763487</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133576030</v>
+        <v>133576004</v>
       </c>
       <c r="B23" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396360</v>
+        <v>396364</v>
       </c>
       <c r="R23" t="n">
-        <v>6763487</v>
+        <v>6763588</v>
       </c>
       <c r="S23" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133576055</v>
+        <v>133576037</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>396289</v>
+        <v>396403</v>
       </c>
       <c r="R27" t="n">
-        <v>6763159</v>
+        <v>6763437</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,7 +3502,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133576067</v>
+        <v>133576055</v>
       </c>
       <c r="B28" t="n">
         <v>79333</v>
@@ -3540,7 +3540,7 @@
         <v>396289</v>
       </c>
       <c r="R28" t="n">
-        <v>6763002</v>
+        <v>6763159</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133576037</v>
+        <v>133576067</v>
       </c>
       <c r="B29" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>396403</v>
+        <v>396289</v>
       </c>
       <c r="R29" t="n">
-        <v>6763437</v>
+        <v>6763002</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133575977</v>
+        <v>133575964</v>
       </c>
       <c r="B40" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396433</v>
+        <v>396477</v>
       </c>
       <c r="R40" t="n">
-        <v>6763424</v>
+        <v>6763372</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133575958</v>
+        <v>133575977</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396497</v>
+        <v>396433</v>
       </c>
       <c r="R41" t="n">
-        <v>6763304</v>
+        <v>6763424</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5000,10 +5000,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133575964</v>
+        <v>133575958</v>
       </c>
       <c r="B42" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396477</v>
+        <v>396497</v>
       </c>
       <c r="R42" t="n">
-        <v>6763372</v>
+        <v>6763304</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5107,10 +5107,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133576050</v>
+        <v>133576059</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5142,13 +5142,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396392</v>
+        <v>396159</v>
       </c>
       <c r="R43" t="n">
-        <v>6763248</v>
+        <v>6763076</v>
       </c>
       <c r="S43" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133575953</v>
+        <v>133576058</v>
       </c>
       <c r="B44" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5225,21 +5225,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5249,13 +5249,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396486</v>
+        <v>396184</v>
       </c>
       <c r="R44" t="n">
-        <v>6763277</v>
+        <v>6763111</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133575991</v>
+        <v>133575953</v>
       </c>
       <c r="B45" t="n">
-        <v>78340</v>
+        <v>79952</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5332,21 +5332,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>396482</v>
+        <v>396486</v>
       </c>
       <c r="R45" t="n">
-        <v>6763495</v>
+        <v>6763277</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133576057</v>
+        <v>133575991</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>78340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5439,21 +5439,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396242</v>
+        <v>396482</v>
       </c>
       <c r="R46" t="n">
-        <v>6763146</v>
+        <v>6763495</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133576059</v>
+        <v>133576050</v>
       </c>
       <c r="B47" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396159</v>
+        <v>396392</v>
       </c>
       <c r="R47" t="n">
-        <v>6763076</v>
+        <v>6763248</v>
       </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133576058</v>
+        <v>133576057</v>
       </c>
       <c r="B48" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396184</v>
+        <v>396242</v>
       </c>
       <c r="R48" t="n">
-        <v>6763111</v>
+        <v>6763146</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5749,32 +5749,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133575955</v>
+        <v>133575957</v>
       </c>
       <c r="B49" t="n">
-        <v>79357</v>
+        <v>79952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5784,13 +5784,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396488</v>
+        <v>396490</v>
       </c>
       <c r="R49" t="n">
-        <v>6763293</v>
+        <v>6763306</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5856,32 +5856,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133575993</v>
+        <v>133575955</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>79357</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5891,13 +5891,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>396451</v>
+        <v>396488</v>
       </c>
       <c r="R50" t="n">
-        <v>6763508</v>
+        <v>6763293</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5963,10 +5963,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133575957</v>
+        <v>133575993</v>
       </c>
       <c r="B51" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5974,21 +5974,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>396490</v>
+        <v>396451</v>
       </c>
       <c r="R51" t="n">
-        <v>6763306</v>
+        <v>6763508</v>
       </c>
       <c r="S51" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6926,10 +6926,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133576073</v>
+        <v>133575965</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6937,21 +6937,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>396343</v>
+        <v>396474</v>
       </c>
       <c r="R60" t="n">
-        <v>6763025</v>
+        <v>6763373</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133575965</v>
+        <v>133576073</v>
       </c>
       <c r="B61" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7068,13 +7068,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>396474</v>
+        <v>396343</v>
       </c>
       <c r="R61" t="n">
-        <v>6763373</v>
+        <v>6763025</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7461,10 +7461,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133576000</v>
+        <v>133575994</v>
       </c>
       <c r="B65" t="n">
-        <v>79923</v>
+        <v>79952</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7472,21 +7472,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396407</v>
+        <v>396439</v>
       </c>
       <c r="R65" t="n">
-        <v>6763575</v>
+        <v>6763508</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,10 +7568,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133575984</v>
+        <v>133576005</v>
       </c>
       <c r="B66" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7579,21 +7579,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396445</v>
+        <v>396349</v>
       </c>
       <c r="R66" t="n">
-        <v>6763456</v>
+        <v>6763575</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,10 +7675,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133575994</v>
+        <v>133575984</v>
       </c>
       <c r="B67" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>396439</v>
+        <v>396445</v>
       </c>
       <c r="R67" t="n">
-        <v>6763508</v>
+        <v>6763456</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133576005</v>
+        <v>133576000</v>
       </c>
       <c r="B68" t="n">
-        <v>79952</v>
+        <v>79923</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7793,21 +7793,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>396349</v>
+        <v>396407</v>
       </c>
       <c r="R68" t="n">
         <v>6763575</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7889,10 +7889,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133576031</v>
+        <v>133575986</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7924,13 +7924,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>396375</v>
+        <v>396455</v>
       </c>
       <c r="R69" t="n">
-        <v>6763463</v>
+        <v>6763482</v>
       </c>
       <c r="S69" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,10 +7996,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133576075</v>
+        <v>133575976</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8007,21 +8007,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,13 +8031,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>396346</v>
+        <v>396433</v>
       </c>
       <c r="R70" t="n">
-        <v>6763061</v>
+        <v>6763412</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,10 +8103,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133575986</v>
+        <v>133576031</v>
       </c>
       <c r="B71" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8114,21 +8114,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,13 +8138,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>396455</v>
+        <v>396375</v>
       </c>
       <c r="R71" t="n">
-        <v>6763482</v>
+        <v>6763463</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8210,10 +8210,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133575976</v>
+        <v>133576075</v>
       </c>
       <c r="B72" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8221,21 +8221,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8245,13 +8245,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396433</v>
+        <v>396346</v>
       </c>
       <c r="R72" t="n">
-        <v>6763412</v>
+        <v>6763061</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8317,10 +8317,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133575966</v>
+        <v>133575961</v>
       </c>
       <c r="B73" t="n">
-        <v>57145</v>
+        <v>79357</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396495</v>
+        <v>396468</v>
       </c>
       <c r="R73" t="n">
-        <v>6763422</v>
+        <v>6763343</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,10 +8424,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133576036</v>
+        <v>133576060</v>
       </c>
       <c r="B74" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8435,21 +8435,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>396401</v>
+        <v>396160</v>
       </c>
       <c r="R74" t="n">
-        <v>6763437</v>
+        <v>6763070</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8531,32 +8531,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133575961</v>
+        <v>133575983</v>
       </c>
       <c r="B75" t="n">
-        <v>79357</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>396468</v>
+        <v>396469</v>
       </c>
       <c r="R75" t="n">
-        <v>6763343</v>
+        <v>6763460</v>
       </c>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8638,7 +8638,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133576060</v>
+        <v>133576072</v>
       </c>
       <c r="B76" t="n">
         <v>79333</v>
@@ -8673,13 +8673,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>396160</v>
+        <v>396322</v>
       </c>
       <c r="R76" t="n">
-        <v>6763070</v>
+        <v>6762975</v>
       </c>
       <c r="S76" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,7 +8745,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133575983</v>
+        <v>133576062</v>
       </c>
       <c r="B77" t="n">
         <v>79333</v>
@@ -8780,13 +8780,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>396469</v>
+        <v>396183</v>
       </c>
       <c r="R77" t="n">
-        <v>6763460</v>
+        <v>6763040</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,7 +8852,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133576072</v>
+        <v>133575995</v>
       </c>
       <c r="B78" t="n">
         <v>79333</v>
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>396322</v>
+        <v>396433</v>
       </c>
       <c r="R78" t="n">
-        <v>6762975</v>
+        <v>6763522</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,7 +8959,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133576062</v>
+        <v>133575972</v>
       </c>
       <c r="B79" t="n">
         <v>79333</v>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396183</v>
+        <v>396434</v>
       </c>
       <c r="R79" t="n">
-        <v>6763040</v>
+        <v>6763395</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9066,32 +9066,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133575995</v>
+        <v>133575966</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9101,13 +9101,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396433</v>
+        <v>396495</v>
       </c>
       <c r="R80" t="n">
-        <v>6763522</v>
+        <v>6763422</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9173,10 +9173,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133575972</v>
+        <v>133575990</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9208,13 +9208,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>396434</v>
+        <v>396482</v>
       </c>
       <c r="R81" t="n">
-        <v>6763395</v>
+        <v>6763496</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9280,7 +9280,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133575990</v>
+        <v>133576036</v>
       </c>
       <c r="B82" t="n">
         <v>79091</v>
@@ -9315,13 +9315,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>396482</v>
+        <v>396401</v>
       </c>
       <c r="R82" t="n">
-        <v>6763496</v>
+        <v>6763437</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9387,10 +9387,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133576064</v>
+        <v>133575962</v>
       </c>
       <c r="B83" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9398,21 +9398,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9422,13 +9422,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>396223</v>
+        <v>396491</v>
       </c>
       <c r="R83" t="n">
-        <v>6762996</v>
+        <v>6763390</v>
       </c>
       <c r="S83" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9494,7 +9494,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133575997</v>
+        <v>133576064</v>
       </c>
       <c r="B84" t="n">
         <v>79333</v>
@@ -9529,13 +9529,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>396428</v>
+        <v>396223</v>
       </c>
       <c r="R84" t="n">
-        <v>6763551</v>
+        <v>6762996</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9601,7 +9601,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133576054</v>
+        <v>133575997</v>
       </c>
       <c r="B85" t="n">
         <v>79333</v>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>396310</v>
+        <v>396428</v>
       </c>
       <c r="R85" t="n">
-        <v>6763166</v>
+        <v>6763551</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9708,7 +9708,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133575979</v>
+        <v>133576054</v>
       </c>
       <c r="B86" t="n">
         <v>79333</v>
@@ -9743,13 +9743,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>396449</v>
+        <v>396310</v>
       </c>
       <c r="R86" t="n">
-        <v>6763444</v>
+        <v>6763166</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9815,32 +9815,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133575996</v>
+        <v>133575979</v>
       </c>
       <c r="B87" t="n">
-        <v>79357</v>
+        <v>79333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9850,13 +9850,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>396433</v>
+        <v>396449</v>
       </c>
       <c r="R87" t="n">
-        <v>6763546</v>
+        <v>6763444</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9922,7 +9922,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133575967</v>
+        <v>133575996</v>
       </c>
       <c r="B88" t="n">
         <v>79357</v>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>396474</v>
+        <v>396433</v>
       </c>
       <c r="R88" t="n">
-        <v>6763373</v>
+        <v>6763546</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10029,32 +10029,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133575962</v>
+        <v>133575967</v>
       </c>
       <c r="B89" t="n">
-        <v>79952</v>
+        <v>79357</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>396491</v>
+        <v>396474</v>
       </c>
       <c r="R89" t="n">
-        <v>6763390</v>
+        <v>6763373</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10136,10 +10136,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133575954</v>
+        <v>133575982</v>
       </c>
       <c r="B90" t="n">
-        <v>79333</v>
+        <v>78999</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10147,21 +10147,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>396484</v>
+        <v>396453</v>
       </c>
       <c r="R90" t="n">
-        <v>6763285</v>
+        <v>6763453</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10243,10 +10243,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133575985</v>
+        <v>133575948</v>
       </c>
       <c r="B91" t="n">
-        <v>79333</v>
+        <v>78999</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10254,21 +10254,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10278,13 +10278,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>396448</v>
+        <v>396527</v>
       </c>
       <c r="R91" t="n">
-        <v>6763476</v>
+        <v>6763278</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10350,10 +10350,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133575982</v>
+        <v>133575954</v>
       </c>
       <c r="B92" t="n">
-        <v>78999</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10361,21 +10361,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>396453</v>
+        <v>396484</v>
       </c>
       <c r="R92" t="n">
-        <v>6763453</v>
+        <v>6763285</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10457,10 +10457,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133575948</v>
+        <v>133575985</v>
       </c>
       <c r="B93" t="n">
-        <v>78999</v>
+        <v>79333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10468,21 +10468,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>396527</v>
+        <v>396448</v>
       </c>
       <c r="R93" t="n">
-        <v>6763278</v>
+        <v>6763476</v>
       </c>
       <c r="S93" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD93" t="b">

--- a/artfynd/A 22782-2026 artfynd.xlsx
+++ b/artfynd/A 22782-2026 artfynd.xlsx
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133576029</v>
+        <v>133575981</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396331</v>
+        <v>396453</v>
       </c>
       <c r="R5" t="n">
-        <v>6763518</v>
+        <v>6763448</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133575989</v>
+        <v>133576002</v>
       </c>
       <c r="B6" t="n">
-        <v>79978</v>
+        <v>79117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396482</v>
+        <v>396399</v>
       </c>
       <c r="R6" t="n">
-        <v>6763495</v>
+        <v>6763573</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133576002</v>
+        <v>133576029</v>
       </c>
       <c r="B7" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396399</v>
+        <v>396331</v>
       </c>
       <c r="R7" t="n">
-        <v>6763573</v>
+        <v>6763518</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133575981</v>
+        <v>133575989</v>
       </c>
       <c r="B8" t="n">
         <v>79978</v>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396453</v>
+        <v>396482</v>
       </c>
       <c r="R8" t="n">
-        <v>6763448</v>
+        <v>6763495</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133576049</v>
+        <v>133575949</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396397</v>
+        <v>396524</v>
       </c>
       <c r="R9" t="n">
-        <v>6763265</v>
+        <v>6763269</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133575949</v>
+        <v>133575968</v>
       </c>
       <c r="B11" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>396524</v>
+        <v>396469</v>
       </c>
       <c r="R11" t="n">
-        <v>6763269</v>
+        <v>6763378</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133575968</v>
+        <v>133576049</v>
       </c>
       <c r="B12" t="n">
-        <v>79025</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>396469</v>
+        <v>396397</v>
       </c>
       <c r="R12" t="n">
-        <v>6763378</v>
+        <v>6763265</v>
       </c>
       <c r="S12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2111,7 +2111,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133576063</v>
+        <v>133575956</v>
       </c>
       <c r="B15" t="n">
         <v>79359</v>
@@ -2146,13 +2146,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396193</v>
+        <v>396487</v>
       </c>
       <c r="R15" t="n">
-        <v>6763033</v>
+        <v>6763296</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,7 +2218,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133575956</v>
+        <v>133576063</v>
       </c>
       <c r="B16" t="n">
         <v>79359</v>
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396487</v>
+        <v>396193</v>
       </c>
       <c r="R16" t="n">
-        <v>6763296</v>
+        <v>6763033</v>
       </c>
       <c r="S16" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133576034</v>
+        <v>133575952</v>
       </c>
       <c r="B18" t="n">
-        <v>79978</v>
+        <v>79949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396386</v>
+        <v>396487</v>
       </c>
       <c r="R18" t="n">
-        <v>6763437</v>
+        <v>6763276</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133575952</v>
+        <v>133576034</v>
       </c>
       <c r="B19" t="n">
-        <v>79949</v>
+        <v>79978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396487</v>
+        <v>396386</v>
       </c>
       <c r="R19" t="n">
-        <v>6763276</v>
+        <v>6763437</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133576004</v>
+        <v>133576030</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,21 +2871,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396364</v>
+        <v>396360</v>
       </c>
       <c r="R22" t="n">
-        <v>6763588</v>
+        <v>6763487</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133576030</v>
+        <v>133576004</v>
       </c>
       <c r="B23" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396360</v>
+        <v>396364</v>
       </c>
       <c r="R23" t="n">
-        <v>6763487</v>
+        <v>6763588</v>
       </c>
       <c r="S23" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133575960</v>
+        <v>133576055</v>
       </c>
       <c r="B24" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,21 +3085,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>396487</v>
+        <v>396289</v>
       </c>
       <c r="R24" t="n">
-        <v>6763334</v>
+        <v>6763159</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133576055</v>
+        <v>133575971</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>396289</v>
+        <v>396434</v>
       </c>
       <c r="R25" t="n">
-        <v>6763159</v>
+        <v>6763391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,7 +3288,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133576069</v>
+        <v>133576037</v>
       </c>
       <c r="B26" t="n">
         <v>79978</v>
@@ -3323,13 +3323,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>396297</v>
+        <v>396403</v>
       </c>
       <c r="R26" t="n">
-        <v>6762989</v>
+        <v>6763437</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133576037</v>
+        <v>133575960</v>
       </c>
       <c r="B27" t="n">
         <v>79978</v>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>396403</v>
+        <v>396487</v>
       </c>
       <c r="R27" t="n">
-        <v>6763437</v>
+        <v>6763334</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133575971</v>
+        <v>133576067</v>
       </c>
       <c r="B28" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>396434</v>
+        <v>396289</v>
       </c>
       <c r="R28" t="n">
-        <v>6763391</v>
+        <v>6763002</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133576067</v>
+        <v>133576069</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,21 +3620,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>396289</v>
+        <v>396297</v>
       </c>
       <c r="R29" t="n">
-        <v>6763002</v>
+        <v>6762989</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3716,10 +3716,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133576056</v>
+        <v>133576065</v>
       </c>
       <c r="B30" t="n">
-        <v>79949</v>
+        <v>79978</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,21 +3727,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396204</v>
+        <v>396276</v>
       </c>
       <c r="R30" t="n">
-        <v>6763126</v>
+        <v>6763004</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133576066</v>
+        <v>133575974</v>
       </c>
       <c r="B31" t="n">
-        <v>79949</v>
+        <v>79978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,21 +3834,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396278</v>
+        <v>396426</v>
       </c>
       <c r="R31" t="n">
-        <v>6763006</v>
+        <v>6763408</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133575950</v>
+        <v>133575963</v>
       </c>
       <c r="B32" t="n">
-        <v>79978</v>
+        <v>79117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3941,21 +3941,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396504</v>
+        <v>396488</v>
       </c>
       <c r="R32" t="n">
-        <v>6763271</v>
+        <v>6763387</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,7 +4037,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133576065</v>
+        <v>133575970</v>
       </c>
       <c r="B33" t="n">
         <v>79978</v>
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396276</v>
+        <v>396448</v>
       </c>
       <c r="R33" t="n">
-        <v>6763004</v>
+        <v>6763384</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4144,10 +4144,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133575963</v>
+        <v>133575950</v>
       </c>
       <c r="B34" t="n">
-        <v>79117</v>
+        <v>79978</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4155,21 +4155,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,13 +4179,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396488</v>
+        <v>396504</v>
       </c>
       <c r="R34" t="n">
-        <v>6763387</v>
+        <v>6763271</v>
       </c>
       <c r="S34" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4251,10 +4251,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133575970</v>
+        <v>133576066</v>
       </c>
       <c r="B35" t="n">
-        <v>79978</v>
+        <v>79949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4262,21 +4262,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396448</v>
+        <v>396278</v>
       </c>
       <c r="R35" t="n">
-        <v>6763384</v>
+        <v>6763006</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4358,10 +4358,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133575974</v>
+        <v>133576056</v>
       </c>
       <c r="B36" t="n">
-        <v>79978</v>
+        <v>79949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4369,21 +4369,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>396426</v>
+        <v>396204</v>
       </c>
       <c r="R36" t="n">
-        <v>6763408</v>
+        <v>6763126</v>
       </c>
       <c r="S36" t="n">
         <v>14</v>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4465,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133576052</v>
+        <v>133575999</v>
       </c>
       <c r="B37" t="n">
-        <v>81341</v>
+        <v>78363</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4500,13 +4500,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>396385</v>
+        <v>396410</v>
       </c>
       <c r="R37" t="n">
-        <v>6763240</v>
+        <v>6763572</v>
       </c>
       <c r="S37" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133575999</v>
+        <v>133576052</v>
       </c>
       <c r="B39" t="n">
-        <v>78363</v>
+        <v>81341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4714,13 +4714,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396410</v>
+        <v>396385</v>
       </c>
       <c r="R39" t="n">
-        <v>6763572</v>
+        <v>6763240</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4786,10 +4786,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133575964</v>
+        <v>133575958</v>
       </c>
       <c r="B40" t="n">
-        <v>79949</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4797,21 +4797,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396477</v>
+        <v>396497</v>
       </c>
       <c r="R40" t="n">
-        <v>6763372</v>
+        <v>6763304</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133575958</v>
+        <v>133575964</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>79949</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396497</v>
+        <v>396477</v>
       </c>
       <c r="R41" t="n">
-        <v>6763304</v>
+        <v>6763372</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5107,10 +5107,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133575953</v>
+        <v>133576050</v>
       </c>
       <c r="B43" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5142,13 +5142,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396486</v>
+        <v>396392</v>
       </c>
       <c r="R43" t="n">
-        <v>6763277</v>
+        <v>6763248</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,10 +5214,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133576059</v>
+        <v>133575991</v>
       </c>
       <c r="B44" t="n">
-        <v>79117</v>
+        <v>78363</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5225,21 +5225,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5249,13 +5249,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396159</v>
+        <v>396482</v>
       </c>
       <c r="R44" t="n">
-        <v>6763076</v>
+        <v>6763495</v>
       </c>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,7 +5321,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133576050</v>
+        <v>133576057</v>
       </c>
       <c r="B45" t="n">
         <v>79359</v>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>396392</v>
+        <v>396242</v>
       </c>
       <c r="R45" t="n">
-        <v>6763248</v>
+        <v>6763146</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133576058</v>
+        <v>133575953</v>
       </c>
       <c r="B46" t="n">
-        <v>79117</v>
+        <v>79978</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5439,21 +5439,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5463,13 +5463,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396184</v>
+        <v>396486</v>
       </c>
       <c r="R46" t="n">
-        <v>6763111</v>
+        <v>6763277</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133575991</v>
+        <v>133576058</v>
       </c>
       <c r="B47" t="n">
-        <v>78363</v>
+        <v>79117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396482</v>
+        <v>396184</v>
       </c>
       <c r="R47" t="n">
-        <v>6763495</v>
+        <v>6763111</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133576057</v>
+        <v>133576059</v>
       </c>
       <c r="B48" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396242</v>
+        <v>396159</v>
       </c>
       <c r="R48" t="n">
-        <v>6763146</v>
+        <v>6763076</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6070,10 +6070,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133575992</v>
+        <v>133575959</v>
       </c>
       <c r="B52" t="n">
-        <v>79359</v>
+        <v>79391</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>396468</v>
+        <v>396502</v>
       </c>
       <c r="R52" t="n">
-        <v>6763503</v>
+        <v>6763304</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,7 +6177,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133575975</v>
+        <v>133575947</v>
       </c>
       <c r="B53" t="n">
         <v>79359</v>
@@ -6212,13 +6212,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>396429</v>
+        <v>396542</v>
       </c>
       <c r="R53" t="n">
-        <v>6763411</v>
+        <v>6763282</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133576051</v>
+        <v>133575980</v>
       </c>
       <c r="B54" t="n">
-        <v>79025</v>
+        <v>79117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>396390</v>
+        <v>396452</v>
       </c>
       <c r="R54" t="n">
-        <v>6763254</v>
+        <v>6763447</v>
       </c>
       <c r="S54" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133576061</v>
+        <v>133575992</v>
       </c>
       <c r="B55" t="n">
-        <v>81341</v>
+        <v>79359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,21 +6402,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6426,13 +6426,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>396175</v>
+        <v>396468</v>
       </c>
       <c r="R55" t="n">
-        <v>6763055</v>
+        <v>6763503</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133575947</v>
+        <v>133576061</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>81341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6509,21 +6509,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>396542</v>
+        <v>396175</v>
       </c>
       <c r="R56" t="n">
-        <v>6763282</v>
+        <v>6763055</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6605,10 +6605,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133575959</v>
+        <v>133576051</v>
       </c>
       <c r="B57" t="n">
-        <v>79391</v>
+        <v>79025</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6616,21 +6616,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>396502</v>
+        <v>396390</v>
       </c>
       <c r="R57" t="n">
-        <v>6763304</v>
+        <v>6763254</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6712,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133575980</v>
+        <v>133575975</v>
       </c>
       <c r="B58" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6747,13 +6747,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>396452</v>
+        <v>396429</v>
       </c>
       <c r="R58" t="n">
-        <v>6763447</v>
+        <v>6763411</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6926,7 +6926,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133576073</v>
+        <v>133575951</v>
       </c>
       <c r="B60" t="n">
         <v>79359</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>396343</v>
+        <v>396498</v>
       </c>
       <c r="R60" t="n">
-        <v>6763025</v>
+        <v>6763262</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7033,10 +7033,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133575965</v>
+        <v>133576073</v>
       </c>
       <c r="B61" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7068,13 +7068,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>396474</v>
+        <v>396343</v>
       </c>
       <c r="R61" t="n">
-        <v>6763373</v>
+        <v>6763025</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,10 +7140,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133575951</v>
+        <v>133575965</v>
       </c>
       <c r="B62" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7151,21 +7151,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>396498</v>
+        <v>396474</v>
       </c>
       <c r="R62" t="n">
-        <v>6763262</v>
+        <v>6763373</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7354,10 +7354,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133576000</v>
+        <v>133576005</v>
       </c>
       <c r="B64" t="n">
-        <v>79949</v>
+        <v>79978</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7365,21 +7365,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>396407</v>
+        <v>396349</v>
       </c>
       <c r="R64" t="n">
         <v>6763575</v>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7461,10 +7461,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133575994</v>
+        <v>133576000</v>
       </c>
       <c r="B65" t="n">
-        <v>79978</v>
+        <v>79949</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7472,21 +7472,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396439</v>
+        <v>396407</v>
       </c>
       <c r="R65" t="n">
-        <v>6763508</v>
+        <v>6763575</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,10 +7568,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133575984</v>
+        <v>133576033</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>79025</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7579,21 +7579,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396445</v>
+        <v>396386</v>
       </c>
       <c r="R66" t="n">
-        <v>6763456</v>
+        <v>6763437</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,10 +7675,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133576033</v>
+        <v>133575994</v>
       </c>
       <c r="B67" t="n">
-        <v>79025</v>
+        <v>79978</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7686,21 +7686,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>396386</v>
+        <v>396439</v>
       </c>
       <c r="R67" t="n">
-        <v>6763437</v>
+        <v>6763508</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133576005</v>
+        <v>133575984</v>
       </c>
       <c r="B68" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7793,21 +7793,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>396349</v>
+        <v>396445</v>
       </c>
       <c r="R68" t="n">
-        <v>6763575</v>
+        <v>6763456</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7889,10 +7889,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133575986</v>
+        <v>133576075</v>
       </c>
       <c r="B69" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>396455</v>
+        <v>396346</v>
       </c>
       <c r="R69" t="n">
-        <v>6763482</v>
+        <v>6763061</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,10 +7996,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133575976</v>
+        <v>133576031</v>
       </c>
       <c r="B70" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8007,21 +8007,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,13 +8031,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>396433</v>
+        <v>396375</v>
       </c>
       <c r="R70" t="n">
-        <v>6763412</v>
+        <v>6763463</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,10 +8103,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133576031</v>
+        <v>133575976</v>
       </c>
       <c r="B71" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8114,21 +8114,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,13 +8138,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>396375</v>
+        <v>396433</v>
       </c>
       <c r="R71" t="n">
-        <v>6763463</v>
+        <v>6763412</v>
       </c>
       <c r="S71" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8210,10 +8210,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133576075</v>
+        <v>133575986</v>
       </c>
       <c r="B72" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8221,21 +8221,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396346</v>
+        <v>396455</v>
       </c>
       <c r="R72" t="n">
-        <v>6763061</v>
+        <v>6763482</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8317,10 +8317,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133576036</v>
+        <v>133575995</v>
       </c>
       <c r="B73" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396401</v>
+        <v>396433</v>
       </c>
       <c r="R73" t="n">
-        <v>6763437</v>
+        <v>6763522</v>
       </c>
       <c r="S73" t="n">
         <v>8</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8531,10 +8531,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133576062</v>
+        <v>133576036</v>
       </c>
       <c r="B75" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8542,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,13 +8566,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>396183</v>
+        <v>396401</v>
       </c>
       <c r="R75" t="n">
-        <v>6763040</v>
+        <v>6763437</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8638,10 +8638,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133575972</v>
+        <v>133575990</v>
       </c>
       <c r="B76" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8649,21 +8649,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8673,13 +8673,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>396434</v>
+        <v>396482</v>
       </c>
       <c r="R76" t="n">
-        <v>6763395</v>
+        <v>6763496</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,7 +8745,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133575983</v>
+        <v>133576072</v>
       </c>
       <c r="B77" t="n">
         <v>79359</v>
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>396469</v>
+        <v>396322</v>
       </c>
       <c r="R77" t="n">
-        <v>6763460</v>
+        <v>6762975</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,7 +8852,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133576072</v>
+        <v>133575972</v>
       </c>
       <c r="B78" t="n">
         <v>79359</v>
@@ -8887,10 +8887,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>396322</v>
+        <v>396434</v>
       </c>
       <c r="R78" t="n">
-        <v>6762975</v>
+        <v>6763395</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,10 +8959,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133575990</v>
+        <v>133575983</v>
       </c>
       <c r="B79" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8970,21 +8970,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396482</v>
+        <v>396469</v>
       </c>
       <c r="R79" t="n">
-        <v>6763496</v>
+        <v>6763460</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9066,32 +9066,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133575966</v>
+        <v>133576060</v>
       </c>
       <c r="B80" t="n">
-        <v>57162</v>
+        <v>79359</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9101,13 +9101,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396495</v>
+        <v>396160</v>
       </c>
       <c r="R80" t="n">
-        <v>6763422</v>
+        <v>6763070</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9173,7 +9173,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133576060</v>
+        <v>133576062</v>
       </c>
       <c r="B81" t="n">
         <v>79359</v>
@@ -9208,13 +9208,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>396160</v>
+        <v>396183</v>
       </c>
       <c r="R81" t="n">
-        <v>6763070</v>
+        <v>6763040</v>
       </c>
       <c r="S81" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9280,32 +9280,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133575995</v>
+        <v>133575966</v>
       </c>
       <c r="B82" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,13 +9315,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>396433</v>
+        <v>396495</v>
       </c>
       <c r="R82" t="n">
-        <v>6763522</v>
+        <v>6763422</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9387,32 +9387,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133575996</v>
+        <v>133575997</v>
       </c>
       <c r="B83" t="n">
-        <v>79383</v>
+        <v>79359</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9422,13 +9422,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>396433</v>
+        <v>396428</v>
       </c>
       <c r="R83" t="n">
-        <v>6763546</v>
+        <v>6763551</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9494,32 +9494,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133575997</v>
+        <v>133575996</v>
       </c>
       <c r="B84" t="n">
-        <v>79359</v>
+        <v>79383</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9529,13 +9529,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>396428</v>
+        <v>396433</v>
       </c>
       <c r="R84" t="n">
-        <v>6763551</v>
+        <v>6763546</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9601,32 +9601,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133576054</v>
+        <v>133575967</v>
       </c>
       <c r="B85" t="n">
-        <v>79359</v>
+        <v>79383</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>396310</v>
+        <v>396474</v>
       </c>
       <c r="R85" t="n">
-        <v>6763166</v>
+        <v>6763373</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9815,32 +9815,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133575967</v>
+        <v>133576054</v>
       </c>
       <c r="B87" t="n">
-        <v>79383</v>
+        <v>79359</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9850,13 +9850,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>396474</v>
+        <v>396310</v>
       </c>
       <c r="R87" t="n">
-        <v>6763373</v>
+        <v>6763166</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10350,7 +10350,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133575954</v>
+        <v>133575985</v>
       </c>
       <c r="B92" t="n">
         <v>79359</v>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>396484</v>
+        <v>396448</v>
       </c>
       <c r="R92" t="n">
-        <v>6763285</v>
+        <v>6763476</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10457,7 +10457,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133575985</v>
+        <v>133575954</v>
       </c>
       <c r="B93" t="n">
         <v>79359</v>
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>396448</v>
+        <v>396484</v>
       </c>
       <c r="R93" t="n">
-        <v>6763476</v>
+        <v>6763285</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD93" t="b">

--- a/artfynd/A 22782-2026 artfynd.xlsx
+++ b/artfynd/A 22782-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128349516</v>
+        <v>133575959</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,57 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brattåsen, Hållbrosflötten  Lima socken, Dlr</t>
+          <t>Västra brattåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396342</v>
+        <v>396502</v>
       </c>
       <c r="R2" t="n">
-        <v>6763065</v>
+        <v>6763304</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,80 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Svensson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Svensson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128349527</v>
+        <v>133575948</v>
       </c>
       <c r="B3" t="n">
-        <v>57552</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102622</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ruvande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brattåsen, Hållbrosflötten  Lima socken, Dlr</t>
+          <t>Västra brattåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396342</v>
+        <v>396527</v>
       </c>
       <c r="R3" t="n">
-        <v>6763065</v>
+        <v>6763278</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Pärluggla ruvande i ett gamalt Spillkråkehål, 150m från spillkråkans nya bohål.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Svensson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Svensson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133575969</v>
+        <v>133575968</v>
       </c>
       <c r="B4" t="n">
-        <v>79978</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396453</v>
+        <v>396469</v>
       </c>
       <c r="R4" t="n">
-        <v>6763380</v>
+        <v>6763378</v>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133575981</v>
+        <v>133575982</v>
       </c>
       <c r="B5" t="n">
-        <v>79978</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,7 +1034,7 @@
         <v>396453</v>
       </c>
       <c r="R5" t="n">
-        <v>6763448</v>
+        <v>6763453</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133576002</v>
+        <v>133576033</v>
       </c>
       <c r="B6" t="n">
-        <v>79117</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396399</v>
+        <v>396386</v>
       </c>
       <c r="R6" t="n">
-        <v>6763573</v>
+        <v>6763437</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133576029</v>
+        <v>133576051</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396331</v>
+        <v>396390</v>
       </c>
       <c r="R7" t="n">
-        <v>6763518</v>
+        <v>6763254</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133575989</v>
+        <v>133576027</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>81355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396482</v>
+        <v>396298</v>
       </c>
       <c r="R8" t="n">
-        <v>6763495</v>
+        <v>6763543</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133575949</v>
+        <v>133576052</v>
       </c>
       <c r="B9" t="n">
-        <v>79978</v>
+        <v>81355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396524</v>
+        <v>396385</v>
       </c>
       <c r="R9" t="n">
-        <v>6763269</v>
+        <v>6763240</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133575973</v>
+        <v>133576061</v>
       </c>
       <c r="B10" t="n">
-        <v>79117</v>
+        <v>81355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>396430</v>
+        <v>396175</v>
       </c>
       <c r="R10" t="n">
-        <v>6763401</v>
+        <v>6763055</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133575968</v>
+        <v>133575946</v>
       </c>
       <c r="B11" t="n">
-        <v>79025</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>396469</v>
+        <v>396547</v>
       </c>
       <c r="R11" t="n">
-        <v>6763378</v>
+        <v>6763287</v>
       </c>
       <c r="S11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133576049</v>
+        <v>133575947</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1825,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>396397</v>
+        <v>396542</v>
       </c>
       <c r="R12" t="n">
-        <v>6763265</v>
+        <v>6763282</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1860,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133576032</v>
+        <v>133575951</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>396379</v>
+        <v>396498</v>
       </c>
       <c r="R13" t="n">
-        <v>6763458</v>
+        <v>6763262</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,14 +1959,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133575998</v>
+        <v>133575954</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2039,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396426</v>
+        <v>396484</v>
       </c>
       <c r="R14" t="n">
-        <v>6763563</v>
+        <v>6763285</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,11 +2069,11 @@
         <v>133575956</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2218,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133576063</v>
+        <v>133575958</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2253,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396193</v>
+        <v>396497</v>
       </c>
       <c r="R16" t="n">
-        <v>6763033</v>
+        <v>6763304</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133575987</v>
+        <v>133575972</v>
       </c>
       <c r="B17" t="n">
-        <v>79949</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>396478</v>
+        <v>396434</v>
       </c>
       <c r="R17" t="n">
-        <v>6763495</v>
+        <v>6763395</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2395,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133575952</v>
+        <v>133575975</v>
       </c>
       <c r="B18" t="n">
-        <v>79949</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396487</v>
+        <v>396429</v>
       </c>
       <c r="R18" t="n">
-        <v>6763276</v>
+        <v>6763411</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2502,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133576034</v>
+        <v>133575978</v>
       </c>
       <c r="B19" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2574,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396386</v>
+        <v>396447</v>
       </c>
       <c r="R19" t="n">
-        <v>6763437</v>
+        <v>6763436</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2609,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,14 +2601,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133576003</v>
+        <v>133575979</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2681,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396387</v>
+        <v>396449</v>
       </c>
       <c r="R20" t="n">
-        <v>6763575</v>
+        <v>6763444</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2716,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133576068</v>
+        <v>133575983</v>
       </c>
       <c r="B21" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>396300</v>
+        <v>396469</v>
       </c>
       <c r="R21" t="n">
-        <v>6762998</v>
+        <v>6763460</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2823,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133576030</v>
+        <v>133575984</v>
       </c>
       <c r="B22" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,13 +2850,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>396360</v>
+        <v>396445</v>
       </c>
       <c r="R22" t="n">
-        <v>6763487</v>
+        <v>6763456</v>
       </c>
       <c r="S22" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,14 +2922,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133576004</v>
+        <v>133575985</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3002,13 +2957,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>396364</v>
+        <v>396448</v>
       </c>
       <c r="R23" t="n">
-        <v>6763588</v>
+        <v>6763476</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,14 +3029,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133576055</v>
+        <v>133575992</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3109,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>396289</v>
+        <v>396468</v>
       </c>
       <c r="R24" t="n">
-        <v>6763159</v>
+        <v>6763503</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133575971</v>
+        <v>133575993</v>
       </c>
       <c r="B25" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>396434</v>
+        <v>396451</v>
       </c>
       <c r="R25" t="n">
-        <v>6763391</v>
+        <v>6763508</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3251,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133576037</v>
+        <v>133575995</v>
       </c>
       <c r="B26" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3323,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>396403</v>
+        <v>396433</v>
       </c>
       <c r="R26" t="n">
-        <v>6763437</v>
+        <v>6763522</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3358,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,32 +3350,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133575960</v>
+        <v>133575997</v>
       </c>
       <c r="B27" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3430,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>396487</v>
+        <v>396428</v>
       </c>
       <c r="R27" t="n">
-        <v>6763334</v>
+        <v>6763551</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,14 +3457,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133576067</v>
+        <v>133575998</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3537,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>396289</v>
+        <v>396426</v>
       </c>
       <c r="R28" t="n">
-        <v>6763002</v>
+        <v>6763563</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3572,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133576069</v>
+        <v>133576001</v>
       </c>
       <c r="B29" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3644,13 +3599,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>396297</v>
+        <v>396405</v>
       </c>
       <c r="R29" t="n">
-        <v>6762989</v>
+        <v>6763572</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3679,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3689,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3716,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133576065</v>
+        <v>133576003</v>
       </c>
       <c r="B30" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3751,13 +3706,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>396276</v>
+        <v>396387</v>
       </c>
       <c r="R30" t="n">
-        <v>6763004</v>
+        <v>6763575</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3786,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3796,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3823,32 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133575974</v>
+        <v>133576004</v>
       </c>
       <c r="B31" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3858,13 +3813,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>396426</v>
+        <v>396364</v>
       </c>
       <c r="R31" t="n">
-        <v>6763408</v>
+        <v>6763588</v>
       </c>
       <c r="S31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3893,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3903,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,32 +3885,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133575963</v>
+        <v>133576029</v>
       </c>
       <c r="B32" t="n">
-        <v>79117</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3965,13 +3920,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>396488</v>
+        <v>396331</v>
       </c>
       <c r="R32" t="n">
-        <v>6763387</v>
+        <v>6763518</v>
       </c>
       <c r="S32" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4000,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4010,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133575970</v>
+        <v>133576031</v>
       </c>
       <c r="B33" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4072,13 +4027,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>396448</v>
+        <v>396375</v>
       </c>
       <c r="R33" t="n">
-        <v>6763384</v>
+        <v>6763463</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4107,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4117,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4144,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133575950</v>
+        <v>133576045</v>
       </c>
       <c r="B34" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4179,13 +4134,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>396504</v>
+        <v>396410</v>
       </c>
       <c r="R34" t="n">
-        <v>6763271</v>
+        <v>6763319</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4214,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4224,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4251,32 +4206,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133576066</v>
+        <v>133576047</v>
       </c>
       <c r="B35" t="n">
-        <v>79949</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4286,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>396278</v>
+        <v>396405</v>
       </c>
       <c r="R35" t="n">
-        <v>6763006</v>
+        <v>6763309</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4321,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4331,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4358,32 +4313,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133576056</v>
+        <v>133576049</v>
       </c>
       <c r="B36" t="n">
-        <v>79949</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4393,13 +4348,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>396204</v>
+        <v>396397</v>
       </c>
       <c r="R36" t="n">
-        <v>6763126</v>
+        <v>6763265</v>
       </c>
       <c r="S36" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4428,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4438,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4465,32 +4420,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133575999</v>
+        <v>133576050</v>
       </c>
       <c r="B37" t="n">
-        <v>78363</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4500,13 +4455,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>396410</v>
+        <v>396392</v>
       </c>
       <c r="R37" t="n">
-        <v>6763572</v>
+        <v>6763248</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4535,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4545,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4572,14 +4527,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133576071</v>
+        <v>133576053</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4607,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>396310</v>
+        <v>396338</v>
       </c>
       <c r="R38" t="n">
-        <v>6762958</v>
+        <v>6763247</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4642,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4652,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4679,32 +4634,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133576052</v>
+        <v>133576054</v>
       </c>
       <c r="B39" t="n">
-        <v>81341</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4714,13 +4669,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>396385</v>
+        <v>396310</v>
       </c>
       <c r="R39" t="n">
-        <v>6763240</v>
+        <v>6763166</v>
       </c>
       <c r="S39" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4749,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4759,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4786,14 +4741,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133575958</v>
+        <v>133576055</v>
       </c>
       <c r="B40" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4821,13 +4776,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>396497</v>
+        <v>396289</v>
       </c>
       <c r="R40" t="n">
-        <v>6763304</v>
+        <v>6763159</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4856,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4866,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,32 +4848,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133575964</v>
+        <v>133576057</v>
       </c>
       <c r="B41" t="n">
-        <v>79949</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>396477</v>
+        <v>396242</v>
       </c>
       <c r="R41" t="n">
-        <v>6763372</v>
+        <v>6763146</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4963,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4973,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5000,32 +4955,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133575977</v>
+        <v>133576060</v>
       </c>
       <c r="B42" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5035,13 +4990,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>396433</v>
+        <v>396160</v>
       </c>
       <c r="R42" t="n">
-        <v>6763424</v>
+        <v>6763070</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5070,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5080,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5107,14 +5062,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133576050</v>
+        <v>133576062</v>
       </c>
       <c r="B43" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5142,13 +5097,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>396392</v>
+        <v>396183</v>
       </c>
       <c r="R43" t="n">
-        <v>6763248</v>
+        <v>6763040</v>
       </c>
       <c r="S43" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5177,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5187,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,32 +5169,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133575991</v>
+        <v>133576063</v>
       </c>
       <c r="B44" t="n">
-        <v>78363</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5249,13 +5204,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>396482</v>
+        <v>396193</v>
       </c>
       <c r="R44" t="n">
-        <v>6763495</v>
+        <v>6763033</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5284,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5294,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5321,14 +5276,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133576057</v>
+        <v>133576064</v>
       </c>
       <c r="B45" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5356,13 +5311,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>396242</v>
+        <v>396223</v>
       </c>
       <c r="R45" t="n">
-        <v>6763146</v>
+        <v>6762996</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5391,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5401,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,32 +5383,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133575953</v>
+        <v>133576067</v>
       </c>
       <c r="B46" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5463,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>396486</v>
+        <v>396289</v>
       </c>
       <c r="R46" t="n">
-        <v>6763277</v>
+        <v>6763002</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5498,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5508,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5535,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133576058</v>
+        <v>133576071</v>
       </c>
       <c r="B47" t="n">
-        <v>79117</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5570,13 +5525,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>396184</v>
+        <v>396310</v>
       </c>
       <c r="R47" t="n">
-        <v>6763111</v>
+        <v>6762958</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5605,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5615,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5642,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133576059</v>
+        <v>133576072</v>
       </c>
       <c r="B48" t="n">
-        <v>79117</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,13 +5632,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>396159</v>
+        <v>396322</v>
       </c>
       <c r="R48" t="n">
-        <v>6763076</v>
+        <v>6762975</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5712,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5749,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133575957</v>
+        <v>133576073</v>
       </c>
       <c r="B49" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5784,13 +5739,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>396490</v>
+        <v>396343</v>
       </c>
       <c r="R49" t="n">
-        <v>6763306</v>
+        <v>6763025</v>
       </c>
       <c r="S49" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5819,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5829,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5856,14 +5811,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133575993</v>
+        <v>133576075</v>
       </c>
       <c r="B50" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5891,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>396451</v>
+        <v>396346</v>
       </c>
       <c r="R50" t="n">
-        <v>6763508</v>
+        <v>6763061</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5926,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5936,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5966,7 +5921,7 @@
         <v>133575955</v>
       </c>
       <c r="B51" t="n">
-        <v>79383</v>
+        <v>79397</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6070,32 +6025,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133575959</v>
+        <v>133575961</v>
       </c>
       <c r="B52" t="n">
-        <v>79391</v>
+        <v>79397</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6105,13 +6060,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>396502</v>
+        <v>396468</v>
       </c>
       <c r="R52" t="n">
-        <v>6763304</v>
+        <v>6763343</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6140,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6150,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6177,32 +6132,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133575947</v>
+        <v>133575967</v>
       </c>
       <c r="B53" t="n">
-        <v>79359</v>
+        <v>79397</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6212,13 +6167,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>396542</v>
+        <v>396474</v>
       </c>
       <c r="R53" t="n">
-        <v>6763282</v>
+        <v>6763373</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,32 +6239,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133575980</v>
+        <v>133575996</v>
       </c>
       <c r="B54" t="n">
-        <v>79117</v>
+        <v>79397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6319,13 +6274,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>396452</v>
+        <v>396433</v>
       </c>
       <c r="R54" t="n">
-        <v>6763447</v>
+        <v>6763546</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6354,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,32 +6346,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133575992</v>
+        <v>133576026</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>79397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6426,13 +6381,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>396468</v>
+        <v>396298</v>
       </c>
       <c r="R55" t="n">
-        <v>6763503</v>
+        <v>6763542</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6461,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6498,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133576061</v>
+        <v>133576007</v>
       </c>
       <c r="B56" t="n">
-        <v>81341</v>
+        <v>79459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6509,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>6450</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6533,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>396175</v>
+        <v>396333</v>
       </c>
       <c r="R56" t="n">
-        <v>6763055</v>
+        <v>6763597</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6568,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6578,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6605,10 +6560,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133576051</v>
+        <v>133575949</v>
       </c>
       <c r="B57" t="n">
-        <v>79025</v>
+        <v>79992</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6616,21 +6571,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6640,13 +6595,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>396390</v>
+        <v>396524</v>
       </c>
       <c r="R57" t="n">
-        <v>6763254</v>
+        <v>6763269</v>
       </c>
       <c r="S57" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6675,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6685,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6712,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133575975</v>
+        <v>133575950</v>
       </c>
       <c r="B58" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6723,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6747,13 +6702,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>396429</v>
+        <v>396504</v>
       </c>
       <c r="R58" t="n">
-        <v>6763411</v>
+        <v>6763271</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6782,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6792,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6819,10 +6774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133575978</v>
+        <v>133575953</v>
       </c>
       <c r="B59" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6830,21 +6785,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6854,10 +6809,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>396447</v>
+        <v>396486</v>
       </c>
       <c r="R59" t="n">
-        <v>6763436</v>
+        <v>6763277</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6889,7 +6844,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6899,7 +6854,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6926,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133575951</v>
+        <v>133575957</v>
       </c>
       <c r="B60" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6937,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6961,13 +6916,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>396498</v>
+        <v>396490</v>
       </c>
       <c r="R60" t="n">
-        <v>6763262</v>
+        <v>6763306</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6996,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7006,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7033,10 +6988,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133576073</v>
+        <v>133575960</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7044,21 +6999,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7068,13 +7023,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>396343</v>
+        <v>396487</v>
       </c>
       <c r="R61" t="n">
-        <v>6763025</v>
+        <v>6763334</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7103,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7113,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133575965</v>
+        <v>133575962</v>
       </c>
       <c r="B62" t="n">
-        <v>79978</v>
+        <v>79992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7175,13 +7130,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>396474</v>
+        <v>396491</v>
       </c>
       <c r="R62" t="n">
-        <v>6763373</v>
+        <v>6763390</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7210,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7220,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7247,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133576001</v>
+        <v>133575965</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7258,21 +7213,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7282,13 +7237,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>396405</v>
+        <v>396474</v>
       </c>
       <c r="R63" t="n">
-        <v>6763572</v>
+        <v>6763373</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7317,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7327,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7354,10 +7309,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133576005</v>
+        <v>133575969</v>
       </c>
       <c r="B64" t="n">
-        <v>79978</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7389,13 +7344,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>396349</v>
+        <v>396453</v>
       </c>
       <c r="R64" t="n">
-        <v>6763575</v>
+        <v>6763380</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7424,7 +7379,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7434,7 +7389,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7461,10 +7416,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133576000</v>
+        <v>133575970</v>
       </c>
       <c r="B65" t="n">
-        <v>79949</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7472,21 +7427,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7496,10 +7451,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>396407</v>
+        <v>396448</v>
       </c>
       <c r="R65" t="n">
-        <v>6763575</v>
+        <v>6763384</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7531,7 +7486,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7541,7 +7496,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,10 +7523,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133576033</v>
+        <v>133575971</v>
       </c>
       <c r="B66" t="n">
-        <v>79025</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7579,21 +7534,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7603,10 +7558,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>396386</v>
+        <v>396434</v>
       </c>
       <c r="R66" t="n">
-        <v>6763437</v>
+        <v>6763391</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7638,7 +7593,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7603,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,10 +7630,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133575994</v>
+        <v>133575974</v>
       </c>
       <c r="B67" t="n">
-        <v>79978</v>
+        <v>79992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7710,13 +7665,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>396439</v>
+        <v>396426</v>
       </c>
       <c r="R67" t="n">
-        <v>6763508</v>
+        <v>6763408</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7745,7 +7700,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7710,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,10 +7737,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133575984</v>
+        <v>133575976</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7793,21 +7748,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,13 +7772,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>396445</v>
+        <v>396433</v>
       </c>
       <c r="R68" t="n">
-        <v>6763456</v>
+        <v>6763412</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7852,7 +7807,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7817,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7889,10 +7844,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133576075</v>
+        <v>133575977</v>
       </c>
       <c r="B69" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7900,21 +7855,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7924,13 +7879,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>396346</v>
+        <v>396433</v>
       </c>
       <c r="R69" t="n">
-        <v>6763061</v>
+        <v>6763424</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7959,7 +7914,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7969,7 +7924,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,10 +7951,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133576031</v>
+        <v>133575981</v>
       </c>
       <c r="B70" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8007,21 +7962,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8031,13 +7986,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>396375</v>
+        <v>396453</v>
       </c>
       <c r="R70" t="n">
-        <v>6763463</v>
+        <v>6763448</v>
       </c>
       <c r="S70" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8066,7 +8021,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8076,7 +8031,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,10 +8058,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133575976</v>
+        <v>133575986</v>
       </c>
       <c r="B71" t="n">
-        <v>79978</v>
+        <v>79992</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8138,13 +8093,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>396433</v>
+        <v>396455</v>
       </c>
       <c r="R71" t="n">
-        <v>6763412</v>
+        <v>6763482</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8173,7 +8128,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8183,7 +8138,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8210,10 +8165,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133575986</v>
+        <v>133575989</v>
       </c>
       <c r="B72" t="n">
-        <v>79978</v>
+        <v>79992</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8245,13 +8200,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>396455</v>
+        <v>396482</v>
       </c>
       <c r="R72" t="n">
-        <v>6763482</v>
+        <v>6763495</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8280,7 +8235,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8290,7 +8245,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8317,10 +8272,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133575995</v>
+        <v>133575994</v>
       </c>
       <c r="B73" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8328,21 +8283,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8352,13 +8307,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>396433</v>
+        <v>396439</v>
       </c>
       <c r="R73" t="n">
-        <v>6763522</v>
+        <v>6763508</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8387,7 +8342,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8397,7 +8352,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,32 +8379,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133575961</v>
+        <v>133576005</v>
       </c>
       <c r="B74" t="n">
-        <v>79383</v>
+        <v>79992</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8459,13 +8414,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>396468</v>
+        <v>396349</v>
       </c>
       <c r="R74" t="n">
-        <v>6763343</v>
+        <v>6763575</v>
       </c>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8494,7 +8449,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8504,7 +8459,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8531,10 +8486,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133576036</v>
+        <v>133576028</v>
       </c>
       <c r="B75" t="n">
-        <v>79117</v>
+        <v>79992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8542,21 +8497,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8566,13 +8521,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>396401</v>
+        <v>396299</v>
       </c>
       <c r="R75" t="n">
-        <v>6763437</v>
+        <v>6763512</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8601,7 +8556,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8611,7 +8566,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8638,10 +8593,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133575990</v>
+        <v>133576030</v>
       </c>
       <c r="B76" t="n">
-        <v>79117</v>
+        <v>79992</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8649,21 +8604,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8673,13 +8628,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>396482</v>
+        <v>396360</v>
       </c>
       <c r="R76" t="n">
-        <v>6763496</v>
+        <v>6763487</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8708,7 +8663,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8718,7 +8673,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8745,10 +8700,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133576072</v>
+        <v>133576032</v>
       </c>
       <c r="B77" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8756,21 +8711,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8780,13 +8735,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>396322</v>
+        <v>396379</v>
       </c>
       <c r="R77" t="n">
-        <v>6762975</v>
+        <v>6763458</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8815,7 +8770,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8825,7 +8780,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8852,10 +8807,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133575972</v>
+        <v>133576034</v>
       </c>
       <c r="B78" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8863,21 +8818,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8887,10 +8842,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>396434</v>
+        <v>396386</v>
       </c>
       <c r="R78" t="n">
-        <v>6763395</v>
+        <v>6763437</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8922,7 +8877,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8932,7 +8887,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8959,10 +8914,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133575983</v>
+        <v>133576035</v>
       </c>
       <c r="B79" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8970,21 +8925,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8994,13 +8949,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>396469</v>
+        <v>396394</v>
       </c>
       <c r="R79" t="n">
-        <v>6763460</v>
+        <v>6763432</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9029,7 +8984,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9039,7 +8994,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9066,10 +9021,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133576060</v>
+        <v>133576037</v>
       </c>
       <c r="B80" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9077,21 +9032,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9101,13 +9056,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>396160</v>
+        <v>396403</v>
       </c>
       <c r="R80" t="n">
-        <v>6763070</v>
+        <v>6763437</v>
       </c>
       <c r="S80" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9136,7 +9091,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9146,7 +9101,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9173,10 +9128,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133576062</v>
+        <v>133576041</v>
       </c>
       <c r="B81" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9184,21 +9139,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9208,13 +9163,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>396183</v>
+        <v>396425</v>
       </c>
       <c r="R81" t="n">
-        <v>6763040</v>
+        <v>6763377</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9243,7 +9198,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9253,7 +9208,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9280,32 +9235,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133575966</v>
+        <v>133576046</v>
       </c>
       <c r="B82" t="n">
-        <v>57162</v>
+        <v>79992</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,13 +9270,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>396495</v>
+        <v>396409</v>
       </c>
       <c r="R82" t="n">
-        <v>6763422</v>
+        <v>6763319</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9350,7 +9305,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9360,7 +9315,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9387,10 +9342,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133575997</v>
+        <v>133576065</v>
       </c>
       <c r="B83" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9398,21 +9353,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9422,13 +9377,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>396428</v>
+        <v>396276</v>
       </c>
       <c r="R83" t="n">
-        <v>6763551</v>
+        <v>6763004</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9457,7 +9412,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9467,7 +9422,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9494,32 +9449,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133575996</v>
+        <v>133576068</v>
       </c>
       <c r="B84" t="n">
-        <v>79383</v>
+        <v>79992</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9529,13 +9484,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>396433</v>
+        <v>396300</v>
       </c>
       <c r="R84" t="n">
-        <v>6763546</v>
+        <v>6762998</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9564,7 +9519,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9574,7 +9529,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9601,32 +9556,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133575967</v>
+        <v>133576069</v>
       </c>
       <c r="B85" t="n">
-        <v>79383</v>
+        <v>79992</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9636,13 +9591,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>396474</v>
+        <v>396297</v>
       </c>
       <c r="R85" t="n">
-        <v>6763373</v>
+        <v>6762989</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9671,7 +9626,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9681,7 +9636,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9708,32 +9663,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133575962</v>
+        <v>133576043</v>
       </c>
       <c r="B86" t="n">
-        <v>79978</v>
+        <v>80492</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9743,13 +9698,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>396491</v>
+        <v>396423</v>
       </c>
       <c r="R86" t="n">
-        <v>6763390</v>
+        <v>6763359</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9778,7 +9733,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9788,7 +9743,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9815,10 +9770,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133576054</v>
+        <v>133575991</v>
       </c>
       <c r="B87" t="n">
-        <v>79359</v>
+        <v>78377</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9826,21 +9781,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9850,13 +9805,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>396310</v>
+        <v>396482</v>
       </c>
       <c r="R87" t="n">
-        <v>6763166</v>
+        <v>6763495</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9885,7 +9840,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9895,7 +9850,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9922,10 +9877,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133576064</v>
+        <v>133575999</v>
       </c>
       <c r="B88" t="n">
-        <v>79359</v>
+        <v>78377</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,21 +9888,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9957,13 +9912,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>396223</v>
+        <v>396410</v>
       </c>
       <c r="R88" t="n">
-        <v>6762996</v>
+        <v>6763572</v>
       </c>
       <c r="S88" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9992,7 +9947,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10002,7 +9957,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10029,48 +9984,68 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133575979</v>
+        <v>128349516</v>
       </c>
       <c r="B89" t="n">
-        <v>79359</v>
+        <v>57950</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra brattåsen, Dlr</t>
+          <t>Brattåsen, Hållbrosflötten  Lima socken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>396449</v>
+        <v>396342</v>
       </c>
       <c r="R89" t="n">
-        <v>6763444</v>
+        <v>6763065</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10094,22 +10069,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10124,44 +10099,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Svensson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Svensson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133575982</v>
+        <v>133575966</v>
       </c>
       <c r="B90" t="n">
-        <v>79025</v>
+        <v>57162</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10171,13 +10146,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>396453</v>
+        <v>396495</v>
       </c>
       <c r="R90" t="n">
-        <v>6763453</v>
+        <v>6763422</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10206,7 +10181,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10216,7 +10191,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10243,32 +10218,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133575948</v>
+        <v>133575945</v>
       </c>
       <c r="B91" t="n">
-        <v>79025</v>
+        <v>57165</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>102613</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10278,13 +10253,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>396527</v>
+        <v>396620</v>
       </c>
       <c r="R91" t="n">
-        <v>6763278</v>
+        <v>6763294</v>
       </c>
       <c r="S91" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10313,7 +10288,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10323,7 +10298,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10350,48 +10325,68 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133575985</v>
+        <v>128349527</v>
       </c>
       <c r="B92" t="n">
-        <v>79359</v>
+        <v>57785</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>102622</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Västra brattåsen, Dlr</t>
+          <t>Brattåsen, Hållbrosflötten  Lima socken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>396448</v>
+        <v>396342</v>
       </c>
       <c r="R92" t="n">
-        <v>6763476</v>
+        <v>6763065</v>
       </c>
       <c r="S92" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10415,22 +10410,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Pärluggla ruvande i ett gamalt Spillkråkehål, 150m från spillkråkans nya bohål.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10445,22 +10445,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Svensson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Svensson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133575954</v>
+        <v>133575963</v>
       </c>
       <c r="B93" t="n">
-        <v>79359</v>
+        <v>79131</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10468,21 +10468,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10492,13 +10492,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>396484</v>
+        <v>396488</v>
       </c>
       <c r="R93" t="n">
-        <v>6763285</v>
+        <v>6763387</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10561,6 +10561,1932 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>133575973</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>396430</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6763401</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>133575980</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>396452</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6763447</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>133575990</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>396482</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6763496</v>
+      </c>
+      <c r="S96" t="n">
+        <v>9</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>133576002</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>396399</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6763573</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>133576024</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>396298</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6763548</v>
+      </c>
+      <c r="S98" t="n">
+        <v>19</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>133576036</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>396401</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6763437</v>
+      </c>
+      <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>133576038</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>396400</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6763422</v>
+      </c>
+      <c r="S100" t="n">
+        <v>6</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>133576040</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>396422</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6763389</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>133576042</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>396427</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6763358</v>
+      </c>
+      <c r="S102" t="n">
+        <v>16</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>133576058</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>396184</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6763111</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>133576059</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>396159</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6763076</v>
+      </c>
+      <c r="S104" t="n">
+        <v>13</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>133575952</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>396487</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6763276</v>
+      </c>
+      <c r="S105" t="n">
+        <v>6</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>133575964</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>396477</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6763372</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>133575987</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>396478</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6763495</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>133576000</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>396407</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6763575</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>133576025</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>396296</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6763542</v>
+      </c>
+      <c r="S109" t="n">
+        <v>20</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>133576056</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>396204</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6763126</v>
+      </c>
+      <c r="S110" t="n">
+        <v>14</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>133576066</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Västra brattåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>396278</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6763006</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22782-2026 artfynd.xlsx
+++ b/artfynd/A 22782-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AZ111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575959</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575968</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576033</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576051</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576027</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576061</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575946</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575947</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575951</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575954</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575956</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575958</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575972</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575975</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575978</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575979</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575983</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575984</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575985</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575992</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575993</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575995</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575997</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575998</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576001</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576003</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576004</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576029</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576031</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576045</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576047</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576049</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576050</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576053</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576054</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576055</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576057</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576060</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576062</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576063</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576064</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576067</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576071</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576072</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576073</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576075</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575955</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575961</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575967</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575996</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576026</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576007</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575949</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575950</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575953</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6985,6 +7280,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575957</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575960</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7199,6 +7504,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575962</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7306,6 +7616,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575965</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,6 +7728,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575969</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7520,6 +7840,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575970</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7627,6 +7952,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575971</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7734,6 +8064,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575974</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,6 +8176,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575976</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7948,6 +8288,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575977</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8055,6 +8400,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575981</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8162,6 +8512,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575986</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8269,6 +8624,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575989</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8376,6 +8736,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575994</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8483,6 +8848,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576005</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8590,6 +8960,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576028</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8697,6 +9072,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576030</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8804,6 +9184,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576032</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8911,6 +9296,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576034</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9018,6 +9408,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576035</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9125,6 +9520,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576037</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9232,6 +9632,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576041</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9339,6 +9744,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576046</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9446,6 +9856,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576065</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9553,6 +9968,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576068</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9660,6 +10080,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576069</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9767,6 +10192,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576043</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9874,6 +10304,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575991</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9981,6 +10416,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575999</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10108,6 +10548,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349516</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10215,6 +10660,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575966</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10322,6 +10772,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575945</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10454,6 +10909,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349527</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10561,6 +11021,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575963</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10668,6 +11133,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575973</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10775,6 +11245,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575980</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10882,6 +11357,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575990</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10989,6 +11469,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576002</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11096,6 +11581,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576024</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11203,6 +11693,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576036</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11310,6 +11805,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576038</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11417,6 +11917,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576040</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11524,6 +12029,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576042</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11631,6 +12141,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576058</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11738,6 +12253,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576059</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11845,6 +12365,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575952</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11952,6 +12477,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575964</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12059,6 +12589,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133575987</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12166,6 +12701,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576000</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12273,6 +12813,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12380,6 +12925,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576056</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12487,8 +13037,125 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133576066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>